--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-Small-3.2-24B-Instruct-2506/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3106796116504854</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="B2">
-        <v>0.1785714285714286</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="C2">
-        <v>0.3380281690140845</v>
+        <v>0.323943661971831</v>
       </c>
       <c r="D2">
-        <v>0.7175572519083969</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="E2">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
